--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260908.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260908.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.86%</t>
+          <t>10.89%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.32%</t>
+          <t>10.39%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>8.61%</t>
+          <t>8.72%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.53%</t>
+          <t>7.52%</t>
         </is>
       </c>
     </row>
@@ -704,51 +704,51 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.53%</t>
+          <t>5.43%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>BE UN</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>Bloom Energy Corp</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>103,991</t>
+          <t>49,095</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.24%</t>
+          <t>4.51%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>BE UN</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Bloom Energy Corp</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>49,095</t>
+          <t>103,991</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>4.17%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.37%</t>
+          <t>3.32%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.13%</t>
+          <t>3.18%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.03%</t>
+          <t>2.98%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.57%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.23%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.72%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.60%</t>
+          <t>1.59%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.32%</t>
         </is>
       </c>
     </row>
@@ -990,51 +990,51 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>FE US</t>
+          <t>ES US</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>第一能源公司</t>
+          <t>Eversource能源</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>77,101</t>
+          <t>50,160</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>ES US</t>
+          <t>FE US</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Eversource能源</t>
+          <t>第一能源公司</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>50,160</t>
+          <t>77,101</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
@@ -1056,51 +1056,51 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.15%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>TTEK UW</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>德照科技公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>95,263</t>
+          <t>22,258</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>TTEK UW</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>德照科技公司</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>22,258</t>
+          <t>95,263</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.12%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.11%</t>
+          <t>1.09%</t>
         </is>
       </c>
     </row>
@@ -1144,51 +1144,51 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.06%</t>
+          <t>1.03%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>AEE US</t>
+          <t>EIX US</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>阿莫林公司</t>
+          <t>愛迪生國際</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>27,569</t>
+          <t>51,310</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>EIX US</t>
+          <t>AEE US</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>愛迪生國際</t>
+          <t>阿莫林公司</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>51,310</t>
+          <t>27,569</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.91%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.87%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.84%</t>
+          <t>0.83%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1342,46 +1342,46 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>CMS US</t>
+          <t>PCG US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CMS能源</t>
+          <t>太平洋電力瓦斯公司</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>30,691</t>
+          <t>146,245</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>PCG US</t>
+          <t>AGX US</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>太平洋電力瓦斯公司</t>
+          <t>阿根公司</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>146,245</t>
+          <t>4,921</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>AGX US</t>
+          <t>CMS US</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>阿根公司</t>
+          <t>CMS能源</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>4,921</t>
+          <t>30,691</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.68%</t>
+          <t>0.67%</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.58%</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.52%</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.30%</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.06%</t>
+          <t>0.07%</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       <c r="B72" s="3" t="inlineStr"/>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>113,790,053</t>
+          <t>135,948,768</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr"/>
